--- a/analysis/coding_worksheets/決策群組_#401.xlsx
+++ b/analysis/coding_worksheets/決策群組_#401.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG84"/>
+  <dimension ref="A1:AH84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,145 +451,150 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>from</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_HR1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_HR2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Ops1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Ops2</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Mkt1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Mkt2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_HR1</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_HR2</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Ops1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Ops2</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Mkt1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Mkt2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_HR1</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_HR2</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Ops1</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Ops2</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Mkt1</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Mkt2</t>
         </is>
@@ -618,17 +623,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>我選 Nancy</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
@@ -705,6 +712,9 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -731,17 +741,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>我選 Amy</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
@@ -818,6 +830,9 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,17 +859,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>我選 Nancy</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -931,6 +948,9 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -957,18 +977,20 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>因為財務長不僅需要專業知識，更需要團隊合作能力+國際視野！
 因此Nancy 都有符合這些特質！</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
@@ -1045,6 +1067,9 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1071,18 +1096,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Amy 是候選人裡在公司最資深的副總（18年經驗） 對於公司內部流程與文化最熟悉 
 且在爭議解決委員表現很佳，證明有能力協調組織衝突 是個非常具領導力的人選</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
@@ -1159,6 +1186,9 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1185,17 +1215,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>尤其他在本間公司也有擔任許多職位，可以更加知道這些職位的感受，更能體諒他人的不易，達到帶人也帶心的效果</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -1272,6 +1304,9 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1298,17 +1333,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Nancy在OO公司資歷完整，而且有國際差旅和商務諮詢經驗，我認為這是他很大的優勢。Amy也不錯，但若考慮到帶人統御這部分的話，和員工疏遠可能需要更多時間磨合</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
@@ -1385,6 +1422,9 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1411,17 +1451,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>我確實有考慮過Amy不過他缺少能夠帶領人的經驗！</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -1498,6 +1540,9 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1524,17 +1569,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>確實，Nancy有美國分析師經驗，就算是到他國，具備了解不同文化的經驗！</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
@@ -1611,6 +1658,9 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1637,17 +1687,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>提醒大家：選擇 CFO 財務長時，請務必同時檢視候選人是否具備財務專業、領導合作、國際視野、個人經歷與合作特質，確保符合公司需求。</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
@@ -1724,6 +1776,9 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1750,17 +1805,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>沒錯，不然以他注重細節的特質來講，我覺得工作交給他可以很放心</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -1837,6 +1894,9 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1863,17 +1923,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>財務總裁具有最佳的財務專業 Nancy是很棒的人選 但目前為會計副總裁 對於財務知識，遠遠不及擁有18年經驗的財務副總裁Amy</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
@@ -1950,6 +2012,9 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1976,18 +2041,20 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>我得到的消息，提到Amy有專業能力，但是也有員工提到他的風格有點太霸道！
 我覺得曾經身為員工的我，這點會大大扣風！</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
@@ -2064,6 +2131,9 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2090,17 +2160,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>我得到的消息 Nancy 在專案完成後，不會表揚他人 我認為這樣對與最高階財務領導人來說 有失團隊的士氣</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
@@ -2177,6 +2249,9 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2203,18 +2278,20 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>我相信兩位都是有專業財經能力。
 但，我們公司理想財務長條件，更為看重可以獲得下屬支持的領導人，就目前而言，只有Nancy有更為出色帶隊經驗！</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
@@ -2291,6 +2368,9 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2317,18 +2397,20 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>nancy具有會計師資格，是三位候選人當中唯一一位
 加上他有豐富的諮詢經驗，我想這應該能彌補他在財政知識方面可能的不足</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
@@ -2405,6 +2487,9 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2431,17 +2516,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>小提醒：別忘了在最終決策時，同時考量候選人的財務專業、領導合作能力、國際視野、個人經歷，以及合作與信任特質，這些都是理想 CFO 財務長的重要條件。</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -2518,6 +2605,9 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2544,17 +2634,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>確實，但這個部分可以由助理或其他人替補。主要是能夠帶領公司前進的人！</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
@@ -2631,6 +2723,9 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2657,17 +2752,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>如果撇除不會稱讚他人，你對於Nancy有其他意見嗎？</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
@@ -2744,6 +2841,9 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2770,17 +2870,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>在oo公司的工作財務經驗層面 財務長會希望是在資深財務人士</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
@@ -2857,6 +2959,9 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2883,17 +2988,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>不選Amy，主要是她的履歷，沒有讓我看到可以帶領團隊的前景。此外，做事風格霸道，會讓身邊一起工作的人感到不舒服。只有員工是信服領導人，整個公司才有可能往前走，不然，其他員工不願意，領導人一個人推公司也是很難前進！</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
@@ -2970,6 +3077,9 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2996,17 +3106,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>我這邊沒有Amy霸道的資訊 只有他在爭議委員會獲得不錯的評價</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
@@ -3083,6 +3195,9 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3109,17 +3224,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>會計師也是需要具備足夠財經知識！</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
@@ -3196,6 +3313,9 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3222,17 +3342,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>提醒大家：在討論候選人時，持續關注財務專業、領導合作、國際視野、個人經歷及合作特質，確保最終人選能滿足所有核心條件。</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
@@ -3309,6 +3431,9 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3335,17 +3460,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>其實三位學經歷都頗豐富，目前為止我還是覺得，由國際經驗豐富的Nancy來帶領財務部門較好</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
@@ -3422,6 +3549,9 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3448,17 +3578,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>是的 以人格和國際視野上是如此 但是以金融專業的角度 會計副總相較於財務副總 較難勝任財務長</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
@@ -3535,6 +3667,9 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3561,17 +3696,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>他在美國證券交易委員會擔任過分析師，我想他對國際經濟的脈動應該更能掌握</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
@@ -3648,6 +3785,9 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3674,17 +3814,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
@@ -3761,6 +3903,9 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3787,17 +3932,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
@@ -3874,6 +4021,9 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3900,17 +4050,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>是的 但是財務長需要負責的開始財務相關的知識為重 如果今天是選擇會計長 我會選擇Nancy</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
@@ -3987,6 +4139,9 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4013,17 +4168,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
@@ -4100,6 +4257,9 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4126,17 +4286,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>所以目前我跟行銷長都是選Nancy嗎</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
@@ -4213,6 +4375,9 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4239,17 +4404,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>何以見得，兩位都能在財務部門當到副總，背景知識及專業怎可能落差太大</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
@@ -4326,6 +4493,9 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4352,17 +4522,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>提醒大家：不論學經歷或職位，請持續聚焦於候選人在財務專業、領導合作、國際視野、個人經歷與合作特質上的表現，以協助選出最合適的 CFO 財務長。</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
@@ -4439,6 +4611,9 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4465,17 +4640,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>會計也需要學習股票、公司盈利等等！</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
@@ -4552,6 +4729,9 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4578,17 +4758,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
@@ -4665,6 +4847,9 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4691,17 +4876,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>一位是會計部門的副總 一位是財務 需要搞清楚</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
@@ -4778,6 +4965,9 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4804,17 +4994,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>會計和財務是完全不同的科目</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
@@ -4891,6 +5083,9 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4917,17 +5112,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>會計甚至要很細心去比對公司的財務狀況，在年初和年末提出預算和核對決算</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
@@ -5004,6 +5201,9 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5030,17 +5230,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>是的 但財務需要考量的水募資，融資等更多元的事項 會計事務基本可以外包給四大會計事務所處理 例如Google, Apple</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
@@ -5117,6 +5319,9 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5143,17 +5348,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>小提醒：討論過程中，持續關注候選人在財務專業及領導合作等核心條件，確保最終人選能有效勝任 CFO 財務長職責。</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
@@ -5230,6 +5437,9 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5256,17 +5466,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>就我所知道，會計也需要修財經必修科目。你可以提提看兩者真正差異在哪裡？以及這些差異如何影響公司？</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
@@ -5343,6 +5555,9 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5369,17 +5584,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>差異在，財務負責是財務策略，融資，投資決策 決策面實務</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
@@ -5456,6 +5673,9 @@
         <v>0</v>
       </c>
       <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5482,17 +5702,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>會計師可以也有財務報表，甚至比公司其他人更早知道公司營運狀況</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
@@ -5569,6 +5791,9 @@
         <v>0</v>
       </c>
       <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5595,17 +5820,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>會計主要在流程面，低策略性工作 為被動輸出</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
@@ -5682,6 +5909,9 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5708,17 +5938,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>擁有18年財務背景人士的經驗遠大於0財務經驗的會計人士</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
@@ -5795,6 +6027,9 @@
         <v>0</v>
       </c>
       <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5821,17 +6056,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>對於財務長來說 重要的是策略，而非執行 會計基本上是執行類作業 （如記帳, 報稅）而非策略面 （資金配置，風險控管，資本運作）</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
@@ -5908,6 +6145,9 @@
         <v>0</v>
       </c>
       <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5934,17 +6174,19 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>提醒大家：選擇 CFO 財務長時，請持續檢視候選人在財務專業、領導合作、國際視野、個人經歷與合作特質上的能力，確保人選能夠勝任公司的策略與領導需求。</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
@@ -6021,6 +6263,9 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6047,17 +6292,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>我認為他在公司十幾年，也有所目睹，所以是可以主動做出決策。又或者他可以找其他財務背景的人當他的團隊。依照Nancy管理經驗，我相信他能夠帶的好團隊。術業有專攻！</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
@@ -6134,6 +6381,9 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6160,17 +6410,19 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>我認為做為財務最高主管 必須是財務背景出身，而非會計 因為兩者在本質上有非常大的差別</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
@@ -6247,6 +6499,9 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6273,17 +6528,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>我相信有財經經驗的人很多，但是能夠管理好團隊的人很少，但Nancy就是有管理經驗、還有國際視野、財經知識</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
@@ -6360,6 +6617,9 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6386,17 +6646,19 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>有管理經驗 但沒有財務相關經驗 要勝任財務長還是有難度所在</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
@@ -6473,6 +6735,9 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6499,17 +6764,19 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>我同意人資長的看法</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
@@ -6586,6 +6853,9 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6612,17 +6882,19 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Amy 為財務副總，本身也具管理經驗 副總本身為管理階層</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
@@ -6699,6 +6971,9 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6725,17 +7000,19 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>小提醒：在討論過程中，別忘了持續檢視候選人是否同時具備財務專業、領導合作、國際視野、個人經歷與合作特質，以符合CFO財務長的核心條件。</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
@@ -6812,6 +7089,9 @@
         <v>0</v>
       </c>
       <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6838,17 +7118,19 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>三者基本上都是相同管理階層的人士</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
@@ -6925,6 +7207,9 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6951,17 +7236,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>若財務經驗不足，此時就是看上司是否能聽進下屬建議，推動決策</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
@@ -7038,6 +7325,9 @@
         <v>0</v>
       </c>
       <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7064,18 +7354,20 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>如果讓有專頁能力，做事霸道的人當財務長，對員工總是呼之即來，員工很快就不信服，如何帶領團隊走更久遠的路。
 就算他一個人工作能力十足，但一個人是無法帶領大公司的！</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
@@ -7152,6 +7444,9 @@
         <v>0</v>
       </c>
       <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7178,17 +7473,19 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>但以AMY冷漠的個性，員工與他離心，即便他再專業，也不能一人帶飛全部門啊</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
@@ -7265,6 +7562,9 @@
         <v>0</v>
       </c>
       <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7291,17 +7591,19 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>沒錯！Amy已經被員工抱怨他很霸道了。員工對Nancy評價是，嚴格，但是公平待人！</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
@@ -7378,6 +7680,9 @@
         <v>0</v>
       </c>
       <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7404,17 +7709,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>團隊凝聚力也很重要的！</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
@@ -7491,6 +7798,9 @@
         <v>0</v>
       </c>
       <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7517,17 +7827,19 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>小提醒：除了財務專業外，也請持續關注候選人的領導合作特質，這對CFO的團隊管理與公司長遠發展非常重要。</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
@@ -7604,6 +7916,9 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7630,17 +7945,19 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>做事霸道可以短時間內改進 但18年的財務知識是無法短時間補齊 如果今天是一位待人親切的業務副總，我也不能讓他擔任財務長 因為術業有專攻</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
@@ -7717,6 +8034,9 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7743,17 +8063,19 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>而且Amy他開會常常遲到，我想這點很難被人接受，畢竟時間就是錢！</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
@@ -7830,6 +8152,9 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7856,17 +8181,19 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>就連想要改變朋友個性都很難，何況是這種情況！</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
@@ -7943,6 +8270,9 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7969,17 +8299,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>恰恰相反，人格特質是最難改變的吧</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
@@ -8056,6 +8388,9 @@
         <v>0</v>
       </c>
       <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8082,17 +8417,19 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>比起18年的知識來說，人格特質有辦法約束（獎懲制度）但是財務知識與經驗基本無從規範 也無法短期速成</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
@@ -8169,6 +8506,9 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8195,17 +8535,19 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>知識當然無法一瞬間補上，但他有整個部門，公司是一群人不是一個人</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
@@ -8282,6 +8624,9 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8308,17 +8653,19 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>小提醒：請持續聚焦於候選人在財務專業、領導合作、國際視野、個人經歷與合作特質等方面的綜合表現，協助小組選出最能勝任CFO職務的人選。</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
@@ -8395,6 +8742,9 @@
         <v>0</v>
       </c>
       <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8421,17 +8771,19 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>如果各位認為人格特質&gt;公司發展性 那我投Nancy 一票</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
@@ -8508,6 +8860,9 @@
         <v>0</v>
       </c>
       <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8534,17 +8889,19 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>和大家說 世界上有名的CEO 通常都不怎麼友善</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
@@ -8621,6 +8978,9 @@
         <v>0</v>
       </c>
       <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8647,17 +9007,19 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>例如賈伯斯，馬斯克</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
@@ -8734,6 +9096,9 @@
         <v>0</v>
       </c>
       <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8760,17 +9125,19 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>重點需要放在公司的成功</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
@@ -8847,6 +9214,9 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8873,17 +9243,19 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>但我尊重多數的意見</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
@@ -8960,6 +9332,9 @@
         <v>0</v>
       </c>
       <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8986,18 +9361,20 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>如果今天公司只有一位財務專業人士，當然Amy是最佳人選。
 不過，就算Nancy沒有足夠財經知識，它可以招募專業人才，術業有專攻，如此，團隊分工，才能久遠！</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
@@ -9074,6 +9451,9 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9100,17 +9480,19 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>小提醒：在做最後決定前，請再次確認候選人是否同時具備財務專業、領導合作、國際視野、個人經歷與合作特質，這些都是CFO不可或缺的核心條件。</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
@@ -9187,6 +9569,9 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9213,17 +9598,19 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>我相信Nancy願意傾聽這些財務人才意見！並竟他有管理經驗。但是Amy我就不知道了。或許他認為他自己的知識才能對的！</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
@@ -9300,6 +9687,9 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9326,17 +9716,19 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>所以決定Nancy?</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
@@ -9413,6 +9805,9 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9439,17 +9834,19 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>我們公司文化若偏向團隊融洽 良好人格特質 那我認為Nancy 可能是適合我們團隊</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
@@ -9526,6 +9923,9 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9552,17 +9952,19 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>我們最終選擇 Nancy</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
@@ -9639,6 +10041,9 @@
         <v>0</v>
       </c>
       <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9665,17 +10070,19 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>我們最終選擇 Nancy</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
@@ -9752,6 +10159,9 @@
         <v>0</v>
       </c>
       <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9778,17 +10188,19 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>也並非只看重人格特質啦，nancy有美國證交所經歷，我看好他把在國外的經驗帶回來</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
@@ -9865,6 +10277,9 @@
         <v>0</v>
       </c>
       <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9891,17 +10306,19 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>我們最終選擇 Nancy</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
@@ -9978,6 +10395,9 @@
         <v>0</v>
       </c>
       <c r="AG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="n">
         <v>0</v>
       </c>
     </row>
